--- a/docs/planning/QA엑셀-v1/김유석/QA 담양 중대재해 업무 관리 김유석.xlsx
+++ b/docs/planning/QA엑셀-v1/김유석/QA 담양 중대재해 업무 관리 김유석.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'이행 관리'!$A$3:$I$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'이행 관리'!$3:$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'문서 목록'!$A$3:$I$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'문서 목록'!$A$3:$I$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'문서 목록'!$3:$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28,7 +28,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,9 +52,9 @@
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <i val="1"/>
-      <color rgb="007F7F7F"/>
+      <color rgb="000563C1"/>
       <sz val="10.5"/>
+      <u val="single"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
@@ -107,6 +107,12 @@
     <font>
       <name val="맑은 고딕"/>
       <color rgb="00A6A6A6"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <i val="1"/>
+      <color rgb="007F7F7F"/>
       <sz val="10.5"/>
     </font>
   </fonts>
@@ -283,7 +289,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -781,7 +787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H53"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -840,12 +846,12 @@
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>이 파일</t>
+          <t>내 계정</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>이행 관리와 문서 목록을 봅니다. 2025년은 실제 문서, 2026년은 «예시 자료»입니다.</t>
+          <t>QA박안전5 (재난안전과 담당자) · QA하정수5 (내 부서 보건소 담당 공무원)</t>
         </is>
       </c>
       <c r="C5" s="4" t="n"/>
@@ -855,15 +861,15 @@
       <c r="G5" s="4" t="n"/>
       <c r="H5" s="5" t="n"/>
     </row>
-    <row r="6" ht="22" customHeight="1">
+    <row r="6" ht="36" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>줄 수</t>
+          <t>이 파일</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>11줄</t>
+          <t>이행 관리(할 일마다 서류가 있는지)와 문서 목록을 봅니다. 기준연도는 2025년이 기본이고, 서류를 올리고 확인·삭제하는 일은 내가 올린 «김유석_2025 점검 결과» 서류로만 합니다.</t>
         </is>
       </c>
       <c r="C6" s="4" t="n"/>
@@ -876,12 +882,12 @@
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>시트</t>
+          <t>줄 수</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>이행 관리 → 문서 목록</t>
+          <t>12줄</t>
         </is>
       </c>
       <c r="C7" s="4" t="n"/>
@@ -894,12 +900,12 @@
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>테스트 주소</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>(배포 주소를 받으면 채웁니다)</t>
+          <t>시트</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>이행 관리 → 문서 목록</t>
         </is>
       </c>
       <c r="C8" s="4" t="n"/>
@@ -912,10 +918,14 @@
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>브라우저</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="n"/>
+          <t>테스트 주소</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>https://safety.damyang.go.kr/login</t>
+        </is>
+      </c>
       <c r="C9" s="4" t="n"/>
       <c r="D9" s="4" t="n"/>
       <c r="E9" s="4" t="n"/>
@@ -926,7 +936,7 @@
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>기기</t>
+          <t>브라우저</t>
         </is>
       </c>
       <c r="B10" s="7" t="n"/>
@@ -940,10 +950,10 @@
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>시작한 날</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="n"/>
+          <t>기기</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n"/>
       <c r="C11" s="4" t="n"/>
       <c r="D11" s="4" t="n"/>
       <c r="E11" s="4" t="n"/>
@@ -951,82 +961,78 @@
       <c r="G11" s="4" t="n"/>
       <c r="H11" s="5" t="n"/>
     </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>시작한 날</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="4" t="n"/>
+      <c r="E12" s="4" t="n"/>
+      <c r="F12" s="4" t="n"/>
+      <c r="G12" s="4" t="n"/>
+      <c r="H12" s="5" t="n"/>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>이렇게 하면 됩니다</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="21" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>① 브라우저로 위 «테스트 주소»를 엽니다. 시트마다 맨 위에 «새 탭에서 시작» 또는 «같은 탭에서 이어서»가 적혀 있습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="21" customHeight="1">
+    <row r="15" ht="36" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>② 화면 오른쪽 위 이름을 눌러 «누구로» 칸의 사람으로 바꿉니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="21" customHeight="1">
+          <t>① 위 «테스트 주소»에서 받은 아이디·비밀번호로 로그인합니다. 로그인하면 통합 현황 화면으로 갑니다. 5번 틀리면 계정이 잠깁니다 — 담당 개발자에게 풀어 달라고 합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>③ «어디서» 메뉴로 가서 «해 볼 것»대로 눌러 봅니다.</t>
+          <t>② 내 계정 두 개를 창 두 개에 따로 로그인해 둡니다 — 일반 창에는 QA박안전5(재난안전과), 시크릿 창(Ctrl + Shift + N · 맥 Cmd + Shift + N)에는 QA하정수5(담당 공무원). 두 창을 나란히 두면 계정을 바꿀 필요가 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="21" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>④ «이러면 성공»과 같으면 «결과» 칸에서 성공을, 다르면 실패·오류 등을 고릅니다.</t>
+          <t>③ «누구로» 칸에 적힌 계정의 창에서 «어디서» 메뉴로 가서 «해 볼 것»대로 눌러 봅니다.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="21" customHeight="1">
       <c r="A18" s="10" t="inlineStr">
         <is>
+          <t>④ «이러면 성공»과 같으면 «결과» 칸에서 성공을, 다르면 실패·오류 등을 고릅니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="21" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
           <t>⑤ 실패·오류·문의면 «메모»에 한 줄 적고, 필요하면 «사진» 칸에 화면 캡처를 붙여넣습니다.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>결과 고르는 법</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>결과</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>이럴 때 고르세요</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="n"/>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="n"/>
-      <c r="F21" s="4" t="n"/>
-      <c r="G21" s="4" t="n"/>
-      <c r="H21" s="5" t="n"/>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
-        <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>«이러면 성공»대로 된다</t>
         </is>
       </c>
       <c r="C22" s="4" t="n"/>
@@ -1037,14 +1043,14 @@
       <c r="H22" s="5" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>실패</t>
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>성공</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>되긴 하는데 설명과 다르다 — 막혀야 하는데 저장된다, 문구·숫자가 틀리다</t>
+          <t>«이러면 성공»대로 된다</t>
         </is>
       </c>
       <c r="C23" s="4" t="n"/>
@@ -1055,14 +1061,14 @@
       <c r="H23" s="5" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="13" t="inlineStr">
-        <is>
-          <t>오류</t>
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>실패</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>화면이 멈추거나 깨진다, 눌러도 아무 일이 없다, 오류 창이 뜬다</t>
+          <t>되긴 하는데 설명과 다르다 — 막혀야 하는데 저장된다, 문구·숫자가 틀리다</t>
         </is>
       </c>
       <c r="C24" s="4" t="n"/>
@@ -1073,14 +1079,14 @@
       <c r="H24" s="5" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="14" t="inlineStr">
-        <is>
-          <t>보류</t>
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>오류</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>앞 단계가 안 돼서 지금은 못 한다 — 메모에 이유</t>
+          <t>화면이 멈추거나 깨진다, 눌러도 아무 일이 없다, 오류 창이 뜬다</t>
         </is>
       </c>
       <c r="C25" s="4" t="n"/>
@@ -1091,14 +1097,14 @@
       <c r="H25" s="5" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>보류</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>이 환경에서는 볼 수 없다 — 예: 확인할 데이터가 없다</t>
+          <t>앞 단계가 안 돼서 지금은 못 한다 — 메모에 이유</t>
         </is>
       </c>
       <c r="C26" s="4" t="n"/>
@@ -1109,14 +1115,14 @@
       <c r="H26" s="5" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="16" t="inlineStr">
-        <is>
-          <t>문의</t>
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>확인 불가</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>맞는지 헷갈린다 — 메모에 궁금한 점</t>
+          <t>이 환경에서는 볼 수 없다 — 예: 확인할 데이터가 없다</t>
         </is>
       </c>
       <c r="C27" s="4" t="n"/>
@@ -1126,256 +1132,216 @@
       <c r="G27" s="4" t="n"/>
       <c r="H27" s="5" t="n"/>
     </row>
-    <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="9" t="inlineStr">
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>문의</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>맞는지 헷갈린다 — 메모에 궁금한 점</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="4" t="n"/>
+      <c r="H28" s="5" t="n"/>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>사진 붙이는 법</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="21" customHeight="1">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>• 윈도우: Win + Shift + S → 영역 선택 → 엑셀에서 그 줄의 «사진» 칸을 누르고 Ctrl + V</t>
         </is>
       </c>
     </row>
     <row r="31" ht="21" customHeight="1">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>• 맥: Cmd + Ctrl + Shift + 4 → 영역 선택 → 엑셀에서 그 줄의 «사진» 칸을 누르고 Cmd + V</t>
+          <t>• 윈도우: Win + Shift + S → 영역 선택 → 엑셀에서 그 줄의 «사진» 칸을 누르고 Ctrl + V</t>
         </is>
       </c>
     </row>
     <row r="32" ht="21" customHeight="1">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>• 사진이 크면 모서리를 끌어 줄이세요. 사진은 그 줄 «사진» 칸 위에 두면 됩니다 — 취합할 때 줄 번호로 찾습니다.</t>
+          <t>• 맥: Cmd + Ctrl + Shift + 4 → 영역 선택 → 엑셀에서 그 줄의 «사진» 칸을 누르고 Cmd + V</t>
         </is>
       </c>
     </row>
     <row r="33" ht="21" customHeight="1">
       <c r="A33" s="10" t="inlineStr">
         <is>
+          <t>• 사진이 크면 모서리를 끌어 줄이세요. 사진은 그 줄 «사진» 칸 위에 두면 됩니다 — 취합할 때 줄 번호로 찾습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="21" customHeight="1">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
           <t>• 사진은 떠 있는 그대로 두세요(«셀에 배치»로 넣으면 취합할 때 꺼내지 못합니다).</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="9" t="inlineStr">
-        <is>
-          <t>누구로 — 계정 바꾸는 법</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="21" customHeight="1">
-      <c r="A36" s="10" t="inlineStr">
-        <is>
-          <t>• 화면 오른쪽 위 이름을 누르면 사람 목록이 나옵니다. «누구로» 칸의 이름을 누르면 바뀝니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="36" ht="24" customHeight="1">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>누구로 — 내 계정 두 개</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="21" customHeight="1">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>• 계정은 두 개뿐입니다. «누구로» 칸에 계정 이름과 권한이 함께 적혀 있습니다. 비밀번호는 따로 받습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>이름</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>누구</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="n"/>
-      <c r="D37" s="5" t="n"/>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>권한</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="n"/>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>볼 수 있는 것</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>주로 하는 것</t>
         </is>
       </c>
-      <c r="F37" s="4" t="n"/>
-      <c r="G37" s="4" t="n"/>
-      <c r="H37" s="5" t="n"/>
-    </row>
-    <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="17" t="inlineStr">
-        <is>
-          <t>박안전</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>재난안전과 담당자</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="n"/>
-      <c r="D38" s="5" t="n"/>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>대부분 이 계정 — 등록·확인·공문</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="n"/>
       <c r="G38" s="4" t="n"/>
       <c r="H38" s="5" t="n"/>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="17" t="inlineStr">
         <is>
-          <t>하정수</t>
+          <t>QA박안전5</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>물순환사업소 담당자</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="n"/>
-      <c r="D39" s="5" t="n"/>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>자기 부서 일만 한다</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="n"/>
+          <t>재난안전과 담당자</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="n"/>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>모든 부서 · «내 할일»은 전체</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>전 부서 등록·수정 · 확인 · 상신 · 독촉 — 대부분 이 계정</t>
+        </is>
+      </c>
       <c r="G39" s="4" t="n"/>
       <c r="H39" s="5" t="n"/>
     </row>
-    <row r="40" ht="22" customHeight="1">
+    <row r="40" ht="51" customHeight="1">
       <c r="A40" s="17" t="inlineStr">
         <is>
-          <t>정환경</t>
+          <t>QA하정수5</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>환경과 담당자</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="n"/>
-      <c r="D40" s="5" t="n"/>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>남의 부서 것을 못 건드리는지 볼 때</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="n"/>
+          <t>담당 공무원 (내 부서: 보건소)</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="n"/>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>업무 화면은 전 부서, «내 할일»은 나에게 지정된 것만, 위험성평가 부서별 조치표·교육 이수현황은 내 부서만</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>내 부서 일 · 남의 부서 것을 못 건드리는지 확인</t>
+        </is>
+      </c>
       <c r="G40" s="4" t="n"/>
       <c r="H40" s="5" t="n"/>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="17" t="inlineStr">
         <is>
-          <t>오순환</t>
+          <t>QA시스템관리</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>물순환사업소장</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="n"/>
-      <c r="D41" s="5" t="n"/>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>자기 부서를 보고 재촉한다</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="n"/>
+          <t>시스템 관리자 (김유석만)</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="n"/>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>시스템 관리 메뉴</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>시스템 관리 파일 · 공문 반려(결재 대행)</t>
+        </is>
+      </c>
       <c r="G41" s="4" t="n"/>
       <c r="H41" s="5" t="n"/>
     </row>
-    <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="17" t="inlineStr">
-        <is>
-          <t>김중대</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>중대재해팀장</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="n"/>
-      <c r="D42" s="5" t="n"/>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>공문 결재선(검토)을 볼 때</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="n"/>
-      <c r="G42" s="4" t="n"/>
-      <c r="H42" s="5" t="n"/>
-    </row>
-    <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="17" t="inlineStr">
-        <is>
-          <t>홍길동</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>재난안전과장</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="n"/>
-      <c r="D43" s="5" t="n"/>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>보기만 한다 — 등록 버튼이 없는 게 정상</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="n"/>
-      <c r="G43" s="4" t="n"/>
-      <c r="H43" s="5" t="n"/>
-    </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="17" t="inlineStr">
-        <is>
-          <t>김담양</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>군수</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="n"/>
-      <c r="D44" s="5" t="n"/>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>보기만 한다</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="n"/>
-      <c r="G44" s="4" t="n"/>
-      <c r="H44" s="5" t="n"/>
-    </row>
-    <row r="46" ht="24" customHeight="1">
-      <c r="A46" s="9" t="inlineStr">
+    <row r="43" ht="24" customHeight="1">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>같은 서버를 6명이 함께 씁니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="21" customHeight="1">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>• 내가 만드는 것(교육 · 근로자 · 문서 · 위원 등)은 이름 앞에 내 이름을 붙입니다 — 예: «김유석_집합교육». 그래야 내 것을 찾기 쉽습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="21" customHeight="1">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>• 다른 사람이 만든 것은 고치거나 지우지 않습니다. QA박안전5 계정에는 남의 것도 보이는데, 정상입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="21" customHeight="1">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>• 건수·이수율 같은 숫자는 다른 사람이 작업하는 동안 바뀔 수 있습니다. 숫자가 안 맞으면 새로고침해서 한 번 더 보고, 그래도 다르면 «실패».</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="24" customHeight="1">
+      <c r="A48" s="9" t="inlineStr">
         <is>
           <t>알아 두면 좋은 것 (결함이 아닙니다)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="21" customHeight="1">
-      <c r="A47" s="10" t="inlineStr">
-        <is>
-          <t>• 오늘 날짜가 2026-07-16 으로 고정돼 있습니다. 기한·D-day는 이 날 기준입니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="21" customHeight="1">
-      <c r="A48" s="10" t="inlineStr">
-        <is>
-          <t>• 입력한 데이터는 그 브라우저 탭에만 남습니다. 새 탭을 열면 처음 상태로 돌아갑니다(새로고침은 괜찮습니다).</t>
         </is>
       </c>
     </row>
     <row r="49" ht="21" customHeight="1">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>• 파일 첨부는 파일 이름만 남습니다. 실제 파일을 열거나 받을 수는 없습니다.</t>
+          <t>• 기한·D-day는 서버의 오늘 날짜 기준입니다.</t>
         </is>
       </c>
     </row>
@@ -1389,85 +1355,110 @@
     <row r="51" ht="21" customHeight="1">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>• 과장·군수에게 등록·수정 버튼이 없는 것, 결재 승인·반려 버튼이 없는 것(결재는 온나라에서 합니다)은 정상입니다.</t>
+          <t>• «이러면 성공»의 «» 안 문구와 화면 글자가 조금 다르고(띄어쓰기·마침표·어순) 뜻이 같으면 «문의»로 고르고 화면 문구를 메모에 적습니다.</t>
         </is>
       </c>
     </row>
     <row r="52" ht="21" customHeight="1">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>• 2025년 자료는 실제 문서이고, 2026년 자료는 «예시 자료»입니다.</t>
+          <t>• 온나라 연계 전까지 결재는 시스템 안에서 끝납니다 — 상신하면 바로 «결재완료»가 되고 «내부 처리»로 표시됩니다. 결재자가 로그인해 승인할 일은 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="53" ht="21" customHeight="1">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>• ---</t>
+          <t>• 로그인은 30분이 지나면 끊깁니다(작업 중이어도). 다시 로그인하고 이어서 합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="21" customHeight="1">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>• 독촉·재촉 알림은 실제 직원에게 가고 되돌릴 수 없습니다. 내 부서 건만 1건씩 누릅니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="21" customHeight="1">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>• 과장·팀장이 담당자를 지정하는 흐름과 «내 할일»의 ‹자기 부서 전체› 보기는 과장 계정이 없어 이번 QA 범위 밖입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="21" customHeight="1">
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>• 순서를 놓쳤거나 확인할 자료가 서버에 없으면 «확인 불가»를 고르고 메모에 이유를 적습니다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="50">
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="A48:H48"/>
-    <mergeCell ref="A30:H30"/>
+  <mergeCells count="51">
     <mergeCell ref="B9:H9"/>
     <mergeCell ref="A15:H15"/>
+    <mergeCell ref="F41:H41"/>
     <mergeCell ref="A51:H51"/>
     <mergeCell ref="B6:H6"/>
     <mergeCell ref="B24:H24"/>
-    <mergeCell ref="A36:H36"/>
     <mergeCell ref="A49:H49"/>
-    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="D40:E40"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="E41:H41"/>
+    <mergeCell ref="A45:H45"/>
     <mergeCell ref="B5:H5"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="F38:H38"/>
     <mergeCell ref="B26:H26"/>
     <mergeCell ref="B4:H4"/>
     <mergeCell ref="A16:H16"/>
-    <mergeCell ref="E43:H43"/>
-    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="A54:H54"/>
     <mergeCell ref="B7:H7"/>
     <mergeCell ref="B25:H25"/>
+    <mergeCell ref="A37:H37"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="E42:H42"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="A46:H46"/>
     <mergeCell ref="A18:H18"/>
     <mergeCell ref="B22:H22"/>
     <mergeCell ref="A50:H50"/>
-    <mergeCell ref="E39:H39"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="A56:H56"/>
+    <mergeCell ref="A55:H55"/>
     <mergeCell ref="B27:H27"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B21:H21"/>
-    <mergeCell ref="E38:H38"/>
-    <mergeCell ref="E44:H44"/>
+    <mergeCell ref="B12:H12"/>
     <mergeCell ref="A33:H33"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A47:H47"/>
     <mergeCell ref="B11:H11"/>
+    <mergeCell ref="B40:C40"/>
     <mergeCell ref="A32:H32"/>
     <mergeCell ref="B23:H23"/>
     <mergeCell ref="A17:H17"/>
+    <mergeCell ref="D39:E39"/>
     <mergeCell ref="B8:H8"/>
-    <mergeCell ref="E40:H40"/>
     <mergeCell ref="A53:H53"/>
     <mergeCell ref="A52:H52"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="F40:H40"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A44:H44"/>
     <mergeCell ref="B10:H10"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="B41:C41"/>
     <mergeCell ref="A31:H31"/>
+    <mergeCell ref="B28:H28"/>
+    <mergeCell ref="A34:H34"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"크롬,엣지,웨일,사파리,파이어폭스,기타"</formula1>
     </dataValidation>
-    <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"윈도우 PC,맥,태블릿,휴대폰"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1610,36 +1601,36 @@
         </is>
       </c>
       <c r="B6" s="21">
-        <f>COUNTA('문서 목록'!$A$4:$A$8)</f>
-        <v>5</v>
+        <f>COUNTA('문서 목록'!$A$4:$A$9)</f>
+        <v>6</v>
       </c>
       <c r="C6" s="21">
-        <f>COUNTIF('문서 목록'!$G$4:$G$8,"성공")</f>
+        <f>COUNTIF('문서 목록'!$G$4:$G$9,"성공")</f>
         <v>0</v>
       </c>
       <c r="D6" s="21">
-        <f>COUNTIF('문서 목록'!$G$4:$G$8,"실패")</f>
+        <f>COUNTIF('문서 목록'!$G$4:$G$9,"실패")</f>
         <v>0</v>
       </c>
       <c r="E6" s="21">
-        <f>COUNTIF('문서 목록'!$G$4:$G$8,"오류")</f>
+        <f>COUNTIF('문서 목록'!$G$4:$G$9,"오류")</f>
         <v>0</v>
       </c>
       <c r="F6" s="21">
-        <f>COUNTIF('문서 목록'!$G$4:$G$8,"보류")</f>
+        <f>COUNTIF('문서 목록'!$G$4:$G$9,"보류")</f>
         <v>0</v>
       </c>
       <c r="G6" s="21">
-        <f>COUNTIF('문서 목록'!$G$4:$G$8,"확인 불가")</f>
+        <f>COUNTIF('문서 목록'!$G$4:$G$9,"확인 불가")</f>
         <v>0</v>
       </c>
       <c r="H6" s="21">
-        <f>COUNTIF('문서 목록'!$G$4:$G$8,"문의")</f>
+        <f>COUNTIF('문서 목록'!$G$4:$G$9,"문의")</f>
         <v>0</v>
       </c>
       <c r="I6" s="21">
-        <f>COUNTBLANK('문서 목록'!$G$4:$G$8)</f>
-        <v>5</v>
+        <f>COUNTBLANK('문서 목록'!$G$4:$G$9)</f>
+        <v>6</v>
       </c>
       <c r="J6" s="22">
         <f>IF(B6=0,0,(B6-I6)/B6)</f>
@@ -1654,7 +1645,7 @@
       </c>
       <c r="B7" s="24">
         <f>SUM(B5:B6)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7" s="24">
         <f>SUM(C5:C6)</f>
@@ -1682,7 +1673,7 @@
       </c>
       <c r="I7" s="24">
         <f>SUM(I5:I6)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J7" s="25">
         <f>IF(B7=0,0,(B7-I7)/B7)</f>
@@ -1733,7 +1724,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="38" customWidth="1" min="5" max="5"/>
@@ -1753,7 +1744,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="26" t="inlineStr">
         <is>
-          <t>🗂 새 탭에서 시작하세요.</t>
+          <t>🗂 주로 QA박안전5 창에서 합니다. 4번에서 올린 내 서류로 5·6번을 이어서 하고, 다른 사람이 올린 서류는 확인·반려하지 않습니다.</t>
         </is>
       </c>
     </row>
@@ -1804,13 +1795,13 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="36" customHeight="1">
+    <row r="4" ht="96" customHeight="1">
       <c r="A4" s="28" t="n">
         <v>1</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전5(재난안전과)</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1820,30 +1811,32 @@
       </c>
       <c r="D4" s="17" t="inlineStr">
         <is>
-          <t>화면과 단위 바꾸기</t>
+          <t>첫 화면과 단위 바꾸기</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>군 단위 · 부서 단위 · 관리대상 단위 → [누락 점검] 탭</t>
+          <t>① 메뉴로 들어가 기준연도를 본다
+② 군 단위 · 부서 단위 · 관리대상 단위 탭을 차례로 누른다
+③ [누락 점검] 탭을 누른다</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>기준연도가 2025이고 단위마다 표가 바뀌며 숫자가 맞다</t>
+          <t>왼쪽 메뉴 이름이 «이행 관리»다(«법정 업무 현황»이면 «실패» — 2026-09-28 «이행 관리»로 확정). 기준연도가 2025다. 탭마다 표가 바뀐다. 군 단위·누락 점검 탭의 숫자와 목록 위 «…개» 숫자가 같다(다르면 새로고침 뒤 다시 본다)</t>
         </is>
       </c>
       <c r="G4" s="29" t="n"/>
       <c r="H4" s="7" t="n"/>
       <c r="I4" s="7" t="n"/>
     </row>
-    <row r="5" ht="36" customHeight="1">
+    <row r="5" ht="51" customHeight="1">
       <c r="A5" s="28" t="n">
         <v>2</v>
       </c>
       <c r="B5" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전5(재난안전과)</t>
         </is>
       </c>
       <c r="C5" s="30" t="inlineStr">
@@ -1853,30 +1846,31 @@
       </c>
       <c r="D5" s="17" t="inlineStr">
         <is>
-          <t>상태 칩과 엑셀</t>
+          <t>상태 칩과 엑셀 내려받기</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>부서 단위에서 상태 칩을 누른다 → [엑셀 내려받기]</t>
+          <t>① 군 단위에서 숫자가 0이 아닌 상태 칩(예: 미이행)을 누른다
+② [엑셀 내려받기]</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>칩 숫자와 줄 수가 같고 «…csv 내려받기 (N행)»의 N이 지금 건수와 같다</t>
+          <t>칩의 숫자와 목록 위 «…개 할 일»이 같다. «…csv 내려받기 (…행)» 알림의 행 수도 같은 숫자다</t>
         </is>
       </c>
       <c r="G5" s="29" t="n"/>
       <c r="H5" s="7" t="n"/>
       <c r="I5" s="7" t="n"/>
     </row>
-    <row r="6" ht="51" customHeight="1">
+    <row r="6" ht="81" customHeight="1">
       <c r="A6" s="28" t="n">
         <v>3</v>
       </c>
       <c r="B6" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전5(재난안전과)</t>
         </is>
       </c>
       <c r="C6" s="30" t="inlineStr">
@@ -1886,30 +1880,33 @@
       </c>
       <c r="D6" s="17" t="inlineStr">
         <is>
-          <t>할 일 상세</t>
+          <t>할 일 상세와 쪽 넘기기</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>할 일 하나를 누른다 → 문서 목록 쪽 넘기기(쪽 번호 입력 포함) → [‹ 단계별 이행현황으로]</t>
+          <t>① 서류가 10건 넘는 할 일 줄을 누른다
+② 아래 문서 목록에서 [›]로 다음 쪽
+③ 쪽 번호 칸에 마지막 쪽보다 큰 수를 치고 Enter
+④ [‹ 단계별 이행현황으로]</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>상세가 열리고 쪽 넘기기가 된다. 없는 쪽 번호를 넣어도 빈 화면이 되지 않는다</t>
+          <t>상세가 열리고 쪽이 넘어간다. 너무 큰 쪽 번호는 마지막 쪽으로 가고 빈 화면이 되지 않는다. 돌아가면 보던 목록이 나온다</t>
         </is>
       </c>
       <c r="G6" s="29" t="n"/>
       <c r="H6" s="7" t="n"/>
       <c r="I6" s="7" t="n"/>
     </row>
-    <row r="7" ht="36" customHeight="1">
+    <row r="7" ht="216" customHeight="1">
       <c r="A7" s="28" t="n">
         <v>4</v>
       </c>
       <c r="B7" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전5(재난안전과)</t>
         </is>
       </c>
       <c r="C7" s="30" t="inlineStr">
@@ -1924,25 +1921,30 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>[＋ 서류 올리기] → 빈 채로 [다음] → 채워서 다음 → 할 일 고르기 → 등록</t>
+          <t>① [누락 점검] 탭에서 서류가 0건인 할 일 하나를 고른다 — 목록 맨 위 말고 중간쯤을 골라 다른 사람과 겹치지 않게 하고 이름을 적어 둔다
+② 기준연도 2025 그대로 [＋ 서류 올리기] → 빈 채로 [다음 — 무슨 일인지 고르기 →]
+③ 파일 1개, 문서명 «김유석_2025 점검 결과», 보고일자(2025년 안), «내부 문서», 담당부서·담당자(조직도에서 재난안전과 한 사람)를 채우고 다음
+④ 할 일을 고르지 않고 [다음 — 확인 →]
+⑤ ①의 할 일을 검색해 고르고 [이대로 등록]
+⑥ 결과 창은 [닫기] (되돌리기는 누르지 않는다 — 이 서류를 아래 줄에서 쓴다)</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>빈 칸마다 오류가 표시된다. 등록하면 만든 문서로 가는 링크와 [되돌리기]가 있다</t>
+          <t>빈 칸마다 빨간 안내와 «…확인해 주세요.»가 뜬다. 할 일 없이는 «이 문서가 증빙하는 업무단계를 하나 이상 선택해야 합니다.» 등록하면 결과 창에 만든 문서 링크와 [방금 만든 1건 되돌리기]가 있다</t>
         </is>
       </c>
       <c r="G7" s="29" t="n"/>
       <c r="H7" s="7" t="n"/>
       <c r="I7" s="7" t="n"/>
     </row>
-    <row r="8" ht="51" customHeight="1">
+    <row r="8" ht="156" customHeight="1">
       <c r="A8" s="28" t="n">
         <v>5</v>
       </c>
       <c r="B8" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전5(재난안전과)</t>
         </is>
       </c>
       <c r="C8" s="30" t="inlineStr">
@@ -1952,30 +1954,34 @@
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
-          <t>완료 확인·반려</t>
+          <t>서류 확인 — 반려·완료·되돌리기</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>진행중 할 일 → [확인하기] → 사유 없이 반려 → 사유 넣고 반려 → [확인하기] → [완료 처리] → [확인 되돌리기]</t>
+          <t>① 문서 목록 검색창에 «김유석_2025» → 4번 문서를 열고 위의 할 일 이름을 누른다. 할 일 상세의 문서 목록에 내 서류 한 건만 있을 때만 이어서 한다(다른 사람 서류도 있으면 «확인 불가»)
+② [확인하기] → [확인 반려] → 사유 없이 [확인 반려]
+③ 사유를 적고 [확인 반려]
+④ [확인하기] → [완료 처리]
+⑤ [확인 되돌리기] → [완료 되돌리기]</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>사유 없는 반려는 안 된다. 완료 처리와 되돌리기가 된다</t>
+          <t>사유 없이는 «반려 사유를 입력해야 저장됩니다.» 반려하면 상세에 «확인 반려 — (적은 사유)»가 보인다. 완료 처리하면 «완료 확인됨»과 확인한 사람(QA박안전5 계정)이 보이고, 되돌리면 다시 [확인하기]가 나오며 상태가 처음(진행중)으로 돌아간다</t>
         </is>
       </c>
       <c r="G8" s="29" t="n"/>
       <c r="H8" s="7" t="n"/>
       <c r="I8" s="7" t="n"/>
     </row>
-    <row r="9" ht="36" customHeight="1">
+    <row r="9" ht="81" customHeight="1">
       <c r="A9" s="28" t="n">
         <v>6</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>하정수</t>
+          <t>QA하정수5(담당 공무원)</t>
         </is>
       </c>
       <c r="C9" s="30" t="inlineStr">
@@ -1985,17 +1991,18 @@
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
-          <t>부서 담당자는 확인하지 않는다</t>
+          <t>담당 공무원은 확인·비해당을 못 한다</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>같은 할 일 상세를 연다</t>
+          <t>① QA하정수5 창에서 메뉴로 들어가 첫 화면을 본다
+② QA박안전5 창에 열려 있는 5번 할 일 상세의 주소(끝에 «stage=…»가 붙어 있다)를 복사해 QA하정수5 창 주소창에 붙여 넣고 Enter</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>[확인하기] · 반려 · 비해당 버튼이 없다</t>
+          <t>첫 화면은 «부서 단위»에 내 부서(보건소) 조건이 걸려 내 부서 줄만 보인다. 할 일 상세에는 [확인하기]·[확인 반려]·[비해당 — 사유 기재]가 없다([＋ 서류 올리기]는 있다)</t>
         </is>
       </c>
       <c r="G9" s="29" t="n"/>
@@ -2050,11 +2057,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="38" customWidth="1" min="5" max="5"/>
@@ -2074,7 +2081,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="26" t="inlineStr">
         <is>
-          <t>🗂 어느 탭에서 해도 됩니다.</t>
+          <t>🗂 주로 QA박안전5 창에서 합니다. 미분류 문서는 실제 원장 문서라 분류를 저장하지 않고, 11번에서 내가 만든 서류를 지워 처음 상태로 돌려 둡니다.</t>
         </is>
       </c>
     </row>
@@ -2125,13 +2132,13 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="36" customHeight="1">
+    <row r="4" ht="81" customHeight="1">
       <c r="A4" s="28" t="n">
         <v>7</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전5(재난안전과)</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -2146,25 +2153,28 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>연도 칩 · 검색 · [업무단계 고르기]로 할 일 2개 → 새로고침 → [필터 초기화]</t>
+          <t>① 연도 칩 하나를 누르고 검색창에 낱말을 친다
+② [업무단계 고르기]에서 할 일 2개 → [적용]
+③ 새로고침
+④ [필터 초기화]</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>조건이 새로고침 뒤에도 남고 초기화하면 풀린다</t>
+          <t>조건대로 목록이 줄고, 새로고침 뒤에도 연도·검색어·할 일 2개가 남는다. 초기화하면 풀리고 연도는 기본(2025)으로 돌아간다</t>
         </is>
       </c>
       <c r="G4" s="29" t="n"/>
       <c r="H4" s="7" t="n"/>
       <c r="I4" s="7" t="n"/>
     </row>
-    <row r="5" ht="51" customHeight="1">
+    <row r="5" ht="66" customHeight="1">
       <c r="A5" s="28" t="n">
         <v>8</v>
       </c>
       <c r="B5" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전5(재난안전과)</t>
         </is>
       </c>
       <c r="C5" s="30" t="inlineStr">
@@ -2179,25 +2189,26 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>문서 하나를 연다</t>
+          <t>① 할 일이 붙은 2025 문서 하나를 연다
+② 위의 할 일 이름을 누른다</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>문서번호 · 수발신 · 담당부서 · 데이터 구분 · 연결된 할 일이 보이고, 할 일을 누르면 이행 관리로 간다</t>
+          <t>문서번호 · 수발신 · 담당부서 · 데이터 구분(«문서 원장 실측»)과 연결된 할 일이 보인다. 할 일을 누르면 이행 관리의 그 할 일 상세로 간다</t>
         </is>
       </c>
       <c r="G5" s="29" t="n"/>
       <c r="H5" s="7" t="n"/>
       <c r="I5" s="7" t="n"/>
     </row>
-    <row r="6" ht="36" customHeight="1">
+    <row r="6" ht="126" customHeight="1">
       <c r="A6" s="28" t="n">
         <v>9</v>
       </c>
-      <c r="B6" s="30" t="inlineStr">
-        <is>
-          <t>박안전</t>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>QA박안전5(재난안전과) → QA하정수5(담당 공무원)</t>
         </is>
       </c>
       <c r="C6" s="30" t="inlineStr">
@@ -2207,30 +2218,32 @@
       </c>
       <c r="D6" s="17" t="inlineStr">
         <is>
-          <t>미분류 문서 분류하기</t>
+          <t>미분류 문서 — 분류 붙이기</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>미분류 문서 → [업무단계 지정] → 할 일 하나 → 저장</t>
+          <t>① «미분류» 칩이 붙은 문서 하나를 열고 문서명을 적어 둔다
+② [업무단계 지정] → 아무것도 고르지 않고 [저장] → [취소] (할 일을 골라 저장하지 않는다 — 실제 원장 문서라 되돌릴 수 없다)
+③ QA하정수5 창의 문서 목록에서 ①의 문서명을 검색해 연다</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>«증빙으로 붙었습니다» 후 미분류 표시가 사라진다</t>
+          <t>상세 오른쪽에 «분류 붙이기»와 [업무단계 지정]이 있다. 빈 저장은 «업무단계를 하나 이상 선택해야 저장됩니다.»로 막힌다. QA하정수5 계정에는 버튼 대신 «조회 전용 — 원장 교정은 주관부서(재난안전과) 담당자가 수행합니다.»가 보인다. 미분류 문서가 없으면 «확인 불가» (실제 분류 저장은 원장을 바꾸므로 이 시트에서 확인하지 않는다)</t>
         </is>
       </c>
       <c r="G6" s="29" t="n"/>
       <c r="H6" s="7" t="n"/>
       <c r="I6" s="7" t="n"/>
     </row>
-    <row r="7" ht="36" customHeight="1">
+    <row r="7" ht="81" customHeight="1">
       <c r="A7" s="28" t="n">
         <v>10</v>
       </c>
-      <c r="B7" s="30" t="inlineStr">
-        <is>
-          <t>박안전</t>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>QA박안전5(재난안전과)</t>
         </is>
       </c>
       <c r="C7" s="30" t="inlineStr">
@@ -2245,58 +2258,96 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>할 일이 붙은 2025 문서 → [📄 올해 문서로 등록] → 원본으로 돌아가 다시 누른다</t>
+          <t>① 검색창에 «김유석_2025» → 4번 문서를 연다
+② [📄 올해 문서로 등록]
+③ 새 문서의 «가져온 원본»을 눌러 원본으로 돌아간다
+④ [만든 문서 보기]</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>2026 문서가 생기고, 두 번째에는 새로 만들지 않고 이미 이어받은 문서로 안내한다</t>
+          <t>«…년 문서로 등록했습니다»가 뜨고 올해 문서 «김유석_(올해 연도) 점검 결과»가 생긴다. 원본에는 [📄 올해 문서로 등록] 대신 «이어받기 완료»와 [만든 문서 보기]가 있고, [만든 문서 보기]를 누르면 방금 만든 문서가 열린다</t>
         </is>
       </c>
       <c r="G7" s="29" t="n"/>
       <c r="H7" s="7" t="n"/>
       <c r="I7" s="7" t="n"/>
     </row>
-    <row r="8" ht="36" customHeight="1">
+    <row r="8" ht="126" customHeight="1">
       <c r="A8" s="28" t="n">
         <v>11</v>
       </c>
       <c r="B8" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>업무 관리 왼쪽 메뉴</t>
+          <t>QA박안전5(재난안전과)</t>
+        </is>
+      </c>
+      <c r="C8" s="30" t="inlineStr">
+        <is>
+          <t>업무 관리 &gt; 문서 목록</t>
         </is>
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
-          <t>메뉴 구성</t>
+          <t>내가 만든 서류 지우기</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>업무 관리의 왼쪽 메뉴를 본다</t>
+          <t>① 연도 칩 «전체»에서 검색창에 김유석 → 10번에서 만든 올해 문서를 열고 [문서 삭제] → [삭제]
+② 4번 문서(«김유석_2025 점검 결과»)도 같은 방법으로 지운다
+③ 이행 관리 [누락 점검] 탭에서 4번의 할 일을 찾는다</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>이행 관리와 문서 목록 둘뿐이고 기준문서함은 없다</t>
+          <t>삭제 창이 회수될 할 일 연결을 먼저 알려 주고, 지우면 «문서를 삭제했습니다 — 할 일 연결 1건이 함께 회수되었습니다.» 두 문서가 목록에서 사라지고 4번의 할 일이 다시 누락 점검에 나온다(그 사이 다른 사람이 같은 할 일에 서류를 올렸으면 다시 나오지 않을 수 있다 — 그 경우 문서 목록에서 내 두 문서가 사라졌는지만 본다)</t>
         </is>
       </c>
       <c r="G8" s="29" t="n"/>
       <c r="H8" s="7" t="n"/>
       <c r="I8" s="7" t="n"/>
     </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="28" t="n">
+        <v>12</v>
+      </c>
+      <c r="B9" s="30" t="inlineStr">
+        <is>
+          <t>QA박안전5(재난안전과)</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>업무 관리 왼쪽 메뉴</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>메뉴 구성</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>업무 관리의 왼쪽 메뉴를 본다</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>이행 관리와 문서 목록 둘뿐이고 기준문서함은 없다</t>
+        </is>
+      </c>
+      <c r="G9" s="29" t="n"/>
+      <c r="H9" s="7" t="n"/>
+      <c r="I9" s="7" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:I8"/>
+  <autoFilter ref="A3:I9"/>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
-  <conditionalFormatting sqref="G4:G8">
+  <conditionalFormatting sqref="G4:G9">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="1">
       <formula>"성공"</formula>
     </cfRule>
@@ -2316,13 +2367,13 @@
       <formula>"문의"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H8">
+  <conditionalFormatting sqref="H4:H9">
     <cfRule type="expression" priority="7" dxfId="7">
       <formula>AND(OR($G4="실패",$G4="오류",$G4="문의"),$H4="")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="G4:G8" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="목록에서 고르세요" error="결과는 성공 · 실패 · 오류 · 보류 · 확인 불가 · 문의 중 하나입니다." promptTitle="결과 고르기" prompt="성공 · 실패 · 오류 · 보류 · 확인 불가 · 문의 중에서 고르세요. 실패·오류·문의면 옆 메모에 한 줄." type="list">
+    <dataValidation sqref="G4:G9" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="목록에서 고르세요" error="결과는 성공 · 실패 · 오류 · 보류 · 확인 불가 · 문의 중 하나입니다." promptTitle="결과 고르기" prompt="성공 · 실패 · 오류 · 보류 · 확인 불가 · 문의 중에서 고르세요. 실패·오류·문의면 옆 메모에 한 줄." type="list">
       <formula1>"성공,실패,오류,보류,확인 불가,문의"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2408,7 +2459,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
